--- a/安全库存.xlsx
+++ b/安全库存.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Documents\WXWork\1688855728724396\WeDrive\赛卓电子科技(上海)股份有限公司\交付体系\05OP\03 - 安全库存\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B152DFCB-7CBC-4F84-9D27-54A6C7D33F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9CF06F-87B5-4C52-B928-625A9A2C912D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11357,9 +11357,7 @@
       <c r="F44" s="4">
         <v>0</v>
       </c>
-      <c r="G44" s="4">
-        <v>50000</v>
-      </c>
+      <c r="G44" s="4"/>
       <c r="H44" s="3"/>
       <c r="I44" s="19">
         <v>20000</v>

--- a/安全库存.xlsx
+++ b/安全库存.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Documents\WXWork\1688855728724396\WeDrive\赛卓电子科技(上海)股份有限公司\交付体系\05OP\03 - 安全库存\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9CF06F-87B5-4C52-B928-625A9A2C912D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B152DFCB-7CBC-4F84-9D27-54A6C7D33F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11357,7 +11357,9 @@
       <c r="F44" s="4">
         <v>0</v>
       </c>
-      <c r="G44" s="4"/>
+      <c r="G44" s="4">
+        <v>50000</v>
+      </c>
       <c r="H44" s="3"/>
       <c r="I44" s="19">
         <v>20000</v>

--- a/安全库存.xlsx
+++ b/安全库存.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Documents\WXWork\1688855728724396\WeDrive\赛卓电子科技(上海)股份有限公司\交付体系\05OP\03 - 安全库存\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9CF06F-87B5-4C52-B928-625A9A2C912D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED4DD1B3-B7C4-42E3-8062-A936BC18508E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11357,7 +11357,9 @@
       <c r="F44" s="4">
         <v>0</v>
       </c>
-      <c r="G44" s="4"/>
+      <c r="G44" s="4">
+        <v>50000</v>
+      </c>
       <c r="H44" s="3"/>
       <c r="I44" s="19">
         <v>20000</v>
@@ -11608,7 +11610,7 @@
         <v>25</v>
       </c>
       <c r="G46" s="4">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="19">
@@ -13240,7 +13242,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="4">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="19">

--- a/安全库存.xlsx
+++ b/安全库存.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Documents\WXWork\1688855728724396\WeDrive\赛卓电子科技(上海)股份有限公司\交付体系\05OP\03 - 安全库存\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED4DD1B3-B7C4-42E3-8062-A936BC18508E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9CF06F-87B5-4C52-B928-625A9A2C912D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11357,9 +11357,7 @@
       <c r="F44" s="4">
         <v>0</v>
       </c>
-      <c r="G44" s="4">
-        <v>50000</v>
-      </c>
+      <c r="G44" s="4"/>
       <c r="H44" s="3"/>
       <c r="I44" s="19">
         <v>20000</v>
@@ -11610,7 +11608,7 @@
         <v>25</v>
       </c>
       <c r="G46" s="4">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="19">
@@ -13242,7 +13240,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="4">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="19">
